--- a/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 22,73</t>
+          <t>2,45; 23,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 2,74</t>
+          <t>-27,62; -0,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-78,38; -41,77</t>
+          <t>-77,78; -40,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 23,12</t>
+          <t>5,15; 23,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 2,21</t>
+          <t>-22,55; 3,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-84,3; -65,24</t>
+          <t>-84,55; -64,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 20,88</t>
+          <t>7,0; 20,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,88; -2,62</t>
+          <t>-19,74; -1,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-79,2; -58,14</t>
+          <t>-79,09; -57,37</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 30,92</t>
+          <t>2,73; 30,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,93; 3,46</t>
+          <t>-31,55; -0,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,35; -48,47</t>
+          <t>-90,79; -48,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 30,52</t>
+          <t>5,86; 32,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 2,79</t>
+          <t>-25,76; 4,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,29; -82,26</t>
+          <t>-95,35; -82,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,18; 27,24</t>
+          <t>7,97; 26,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,27; -3,54</t>
+          <t>-22,8; -1,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,38; -71,66</t>
+          <t>-91,29; -68,9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,88; 43,97</t>
+          <t>19,99; 43,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 22,8</t>
+          <t>-3,54; 22,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-54,39; -29,94</t>
+          <t>-54,4; -29,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,15; 51,98</t>
+          <t>28,88; 51,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 31,44</t>
+          <t>7,14; 32,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,42; -17,62</t>
+          <t>-41,41; -17,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,94; 44,54</t>
+          <t>26,86; 44,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 22,94</t>
+          <t>5,1; 23,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-45,1; -26,14</t>
+          <t>-45,01; -27,47</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,75; 96,38</t>
+          <t>32,66; 98,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 47,67</t>
+          <t>-5,7; 47,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,78; -60,61</t>
+          <t>-88,74; -60,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,82; 129,75</t>
+          <t>49,55; 129,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 76,41</t>
+          <t>12,55; 79,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,47; -41,26</t>
+          <t>-73,85; -40,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,87; 96,54</t>
+          <t>46,15; 95,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 49,14</t>
+          <t>9,01; 51,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-79,27; -54,88</t>
+          <t>-78,58; -56,68</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 31,15</t>
+          <t>9,64; 31,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 8,33</t>
+          <t>-21,83; 6,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-66,11; -41,85</t>
+          <t>-65,37; -41,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 21,51</t>
+          <t>2,53; 22,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,98; -4,28</t>
+          <t>-29,51; -4,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-71,1; -51,2</t>
+          <t>-71,42; -50,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 23,61</t>
+          <t>9,29; 23,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,74; -2,88</t>
+          <t>-21,17; -2,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-65,82; -49,93</t>
+          <t>-66,19; -50,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,1; 49,54</t>
+          <t>12,38; 50,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 13,0</t>
+          <t>-28,3; 10,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,95; -64,52</t>
+          <t>-85,75; -62,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 31,4</t>
+          <t>3,2; 32,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,88; -6,08</t>
+          <t>-37,38; -6,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-89,53; -70,63</t>
+          <t>-88,01; -71,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,21; 34,84</t>
+          <t>12,02; 33,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,08; -4,19</t>
+          <t>-27,66; -2,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,58; -71,32</t>
+          <t>-84,99; -71,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 17,17</t>
+          <t>-6,22; 17,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-38,49; -8,53</t>
+          <t>-38,29; -8,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-61,66; -36,56</t>
+          <t>-62,77; -36,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 11,9</t>
+          <t>-11,81; 12,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 10,22</t>
+          <t>-14,65; 10,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,59; -11,89</t>
+          <t>-50,39; -10,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 11,29</t>
+          <t>-6,42; 10,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-22,34; -3,51</t>
+          <t>-23,86; -3,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-50,76; -24,35</t>
+          <t>-52,15; -26,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 23,09</t>
+          <t>-7,31; 23,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -12,23</t>
+          <t>-46,26; -11,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,92; -48,41</t>
+          <t>-74,73; -48,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 16,04</t>
+          <t>-14,09; 17,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 13,51</t>
+          <t>-17,68; 14,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,25; -15,29</t>
+          <t>-61,9; -13,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 14,98</t>
+          <t>-7,39; 14,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,1; -4,6</t>
+          <t>-28,71; -4,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,84; -31,25</t>
+          <t>-63,66; -33,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 44,46</t>
+          <t>-10,62; 39,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 43,42</t>
+          <t>-2,57; 49,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-71,83; -17,69</t>
+          <t>-72,05; -22,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,76; 61,32</t>
+          <t>4,98; 61,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,48; 71,97</t>
+          <t>22,89; 72,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-42,74; 14,45</t>
+          <t>-42,4; 12,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,79; 44,33</t>
+          <t>6,4; 43,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,06; 51,24</t>
+          <t>15,78; 51,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-50,21; -12,01</t>
+          <t>-51,41; -11,99</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 87,02</t>
+          <t>-11,56; 71,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 79,33</t>
+          <t>-2,85; 100,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,2; -38,74</t>
+          <t>-81,0; -43,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9,37; 243,93</t>
+          <t>8,45; 250,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,39; 299,03</t>
+          <t>31,05; 299,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 61,98</t>
+          <t>-61,75; 49,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,02; 95,11</t>
+          <t>8,76; 97,87</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20,71; 113,52</t>
+          <t>20,21; 114,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-67,91; -25,43</t>
+          <t>-67,96; -26,84</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,89; 36,98</t>
+          <t>11,6; 36,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 13,79</t>
+          <t>-25,51; 12,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-50,98; -21,64</t>
+          <t>-48,57; -20,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,27; 31,93</t>
+          <t>4,37; 30,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 20,8</t>
+          <t>-11,55; 21,64</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-40,03; -12,4</t>
+          <t>-40,81; -10,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,99; 30,46</t>
+          <t>11,99; 30,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 14,04</t>
+          <t>-12,47; 13,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-41,71; -20,99</t>
+          <t>-41,74; -20,94</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,91; 64,18</t>
+          <t>15,2; 65,18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 22,65</t>
+          <t>-33,87; 21,33</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-68,66; -35,81</t>
+          <t>-68,27; -33,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,21; 55,24</t>
+          <t>5,81; 52,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 34,81</t>
+          <t>-15,74; 35,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-54,86; -20,32</t>
+          <t>-54,42; -17,87</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,52; 50,69</t>
+          <t>16,07; 49,7</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 22,19</t>
+          <t>-17,29; 20,37</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-57,46; -33,39</t>
+          <t>-57,3; -32,65</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,04; 21,46</t>
+          <t>6,91; 21,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-24,94; -5,89</t>
+          <t>-23,86; -5,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-80,48; -65,03</t>
+          <t>-79,38; -64,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11,73; 29,27</t>
+          <t>11,11; 28,24</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 8,3</t>
+          <t>-12,74; 7,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-69,91; -54,17</t>
+          <t>-70,02; -53,62</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,59; 22,74</t>
+          <t>10,78; 22,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -1,31</t>
+          <t>-15,98; -1,56</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-72,55; -62,03</t>
+          <t>-73,57; -62,18</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,18; 29,56</t>
+          <t>8,28; 29,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,98; -7,47</t>
+          <t>-28,51; -6,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-95,65; -86,91</t>
+          <t>-95,58; -86,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16,02; 47,53</t>
+          <t>14,85; 45,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 13,34</t>
+          <t>-17,43; 12,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-95,04; -83,44</t>
+          <t>-95,22; -83,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,92; 32,59</t>
+          <t>13,62; 32,28</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,84; -2,12</t>
+          <t>-20,72; -2,21</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-94,53; -87,2</t>
+          <t>-94,67; -87,47</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>23,22; 43,75</t>
+          <t>23,77; 43,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>30,6; 49,24</t>
+          <t>30,88; 49,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>15,92; 37,44</t>
+          <t>16,31; 36,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15,31; 33,04</t>
+          <t>15,88; 34,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>18,17; 36,14</t>
+          <t>17,93; 35,44</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,51; 27,97</t>
+          <t>9,0; 28,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,11; 36,43</t>
+          <t>22,09; 35,5</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>26,54; 39,56</t>
+          <t>26,52; 39,8</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>15,19; 29,51</t>
+          <t>15,33; 29,73</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>38,41; 96,32</t>
+          <t>38,98; 96,54</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>49,64; 108,64</t>
+          <t>50,65; 111,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26,2; 80,88</t>
+          <t>27,6; 80,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22,18; 59,75</t>
+          <t>22,75; 64,39</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26,39; 64,96</t>
+          <t>26,24; 64,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,8; 51,18</t>
+          <t>12,94; 50,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,24; 71,71</t>
+          <t>35,07; 66,9</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>41,91; 75,32</t>
+          <t>42,06; 76,85</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24,4; 56,13</t>
+          <t>24,6; 55,93</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>16,35; 24,1</t>
+          <t>16,24; 24,16</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 7,73</t>
+          <t>-0,84; 7,93</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-44,79; -35,05</t>
+          <t>-45,04; -35,21</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14,65; 22,76</t>
+          <t>14,95; 22,75</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,92</t>
+          <t>2,19; 11,4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-40,41; -30,73</t>
+          <t>-40,16; -30,72</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,89; 22,53</t>
+          <t>16,84; 22,39</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,52</t>
+          <t>1,9; 8,06</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-41,11; -34,21</t>
+          <t>-41,31; -34,19</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>22,77; 36,14</t>
+          <t>22,31; 36,13</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 11,5</t>
+          <t>-1,2; 11,88</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-63,86; -51,59</t>
+          <t>-63,35; -51,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20,51; 34,68</t>
+          <t>20,83; 34,33</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,44; 16,38</t>
+          <t>3,19; 17,39</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -45,93</t>
+          <t>-56,98; -45,79</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,7; 33,57</t>
+          <t>23,69; 33,24</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,57</t>
+          <t>2,69; 11,85</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-58,26; -50,45</t>
+          <t>-58,68; -50,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 23,4</t>
+          <t>2,56; 23,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,62; -0,11</t>
+          <t>-27,45; 1,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-77,78; -40,12</t>
+          <t>-78,73; -44,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 23,74</t>
+          <t>5,29; 23,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 3,75</t>
+          <t>-21,33; 3,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-84,55; -64,62</t>
+          <t>-84,75; -64,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 20,49</t>
+          <t>6,77; 20,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,74; -1,46</t>
+          <t>-20,76; -2,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-79,09; -57,37</t>
+          <t>-78,71; -57,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 30,86</t>
+          <t>3,27; 31,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,55; -0,31</t>
+          <t>-31,13; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,79; -48,22</t>
+          <t>-90,9; -55,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 32,17</t>
+          <t>5,89; 32,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 4,29</t>
+          <t>-24,35; 4,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,35; -82,33</t>
+          <t>-94,83; -81,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 26,54</t>
+          <t>7,7; 26,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,8; -1,96</t>
+          <t>-23,98; -3,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,29; -68,9</t>
+          <t>-91,12; -69,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,99; 43,87</t>
+          <t>19,99; 43,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 22,63</t>
+          <t>-3,15; 23,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-54,4; -29,76</t>
+          <t>-54,93; -29,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,88; 51,87</t>
+          <t>30,24; 53,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 32,32</t>
+          <t>5,77; 32,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,41; -17,15</t>
+          <t>-41,61; -17,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,86; 44,43</t>
+          <t>27,15; 44,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 23,91</t>
+          <t>5,38; 24,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-45,01; -27,47</t>
+          <t>-44,03; -26,31</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,66; 98,49</t>
+          <t>32,49; 98,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 47,6</t>
+          <t>-4,75; 52,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,74; -60,68</t>
+          <t>-88,62; -60,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,55; 129,26</t>
+          <t>53,34; 140,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 79,38</t>
+          <t>10,51; 84,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,85; -40,27</t>
+          <t>-73,38; -39,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,15; 95,87</t>
+          <t>46,94; 98,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 51,73</t>
+          <t>9,38; 51,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-78,58; -56,68</t>
+          <t>-78,71; -56,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,64; 31,52</t>
+          <t>9,59; 32,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 6,74</t>
+          <t>-21,79; 7,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-65,37; -41,72</t>
+          <t>-65,9; -42,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 22,64</t>
+          <t>2,22; 22,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,51; -4,23</t>
+          <t>-29,95; -4,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-71,42; -50,72</t>
+          <t>-70,74; -50,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 23,06</t>
+          <t>8,55; 23,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,17; -2,01</t>
+          <t>-21,51; -3,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-66,19; -50,97</t>
+          <t>-65,29; -49,62</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,38; 50,63</t>
+          <t>12,58; 53,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 10,29</t>
+          <t>-28,5; 10,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,75; -62,95</t>
+          <t>-86,41; -64,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 32,26</t>
+          <t>2,96; 31,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,38; -6,06</t>
+          <t>-37,24; -6,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,01; -71,53</t>
+          <t>-88,21; -70,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,02; 33,44</t>
+          <t>10,81; 34,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,66; -2,98</t>
+          <t>-27,6; -4,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,99; -71,76</t>
+          <t>-85,54; -71,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 17,35</t>
+          <t>-5,94; 18,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-38,29; -8,94</t>
+          <t>-38,29; -9,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-62,77; -36,37</t>
+          <t>-62,4; -37,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 12,63</t>
+          <t>-12,13; 12,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 10,93</t>
+          <t>-15,65; 9,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-50,39; -10,17</t>
+          <t>-49,49; -9,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 10,7</t>
+          <t>-5,96; 10,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-23,86; -3,54</t>
+          <t>-22,63; -2,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-52,15; -26,46</t>
+          <t>-51,62; -26,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 23,37</t>
+          <t>-7,12; 25,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -11,84</t>
+          <t>-47,4; -13,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,73; -48,68</t>
+          <t>-74,6; -48,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 17,2</t>
+          <t>-14,18; 16,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 14,3</t>
+          <t>-18,45; 13,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -13,69</t>
+          <t>-61,32; -12,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 14,12</t>
+          <t>-6,95; 13,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,71; -4,47</t>
+          <t>-27,49; -3,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,66; -33,73</t>
+          <t>-63,21; -33,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 39,19</t>
+          <t>-11,11; 43,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 49,41</t>
+          <t>-3,98; 44,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-72,05; -22,8</t>
+          <t>-72,63; -19,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 61,14</t>
+          <t>7,28; 58,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,89; 72,37</t>
+          <t>20,64; 68,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 12,17</t>
+          <t>-43,26; 11,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 43,02</t>
+          <t>5,95; 45,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,78; 51,73</t>
+          <t>17,24; 53,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-51,41; -11,99</t>
+          <t>-50,4; -12,65</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 71,92</t>
+          <t>-11,76; 78,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 100,98</t>
+          <t>-4,27; 90,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,0; -43,53</t>
+          <t>-81,78; -44,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,45; 250,4</t>
+          <t>10,24; 220,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>31,05; 299,77</t>
+          <t>28,11; 250,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,75; 49,74</t>
+          <t>-64,49; 38,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,76; 97,87</t>
+          <t>8,08; 101,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20,21; 114,61</t>
+          <t>22,69; 125,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-67,96; -26,84</t>
+          <t>-67,97; -28,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>11,6; 36,87</t>
+          <t>10,68; 35,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 12,86</t>
+          <t>-23,24; 13,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-48,57; -20,58</t>
+          <t>-51,38; -22,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,37; 30,95</t>
+          <t>6,35; 31,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 21,64</t>
+          <t>-12,49; 21,95</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-40,81; -10,81</t>
+          <t>-41,25; -13,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,99; 30,4</t>
+          <t>11,7; 30,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 13,35</t>
+          <t>-11,99; 13,76</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-41,74; -20,94</t>
+          <t>-40,63; -21,23</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15,2; 65,18</t>
+          <t>14,48; 62,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 21,33</t>
+          <t>-31,06; 21,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-68,27; -33,17</t>
+          <t>-68,62; -36,0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,81; 52,0</t>
+          <t>8,56; 54,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 35,1</t>
+          <t>-16,84; 34,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-54,42; -17,87</t>
+          <t>-55,24; -21,34</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,07; 49,7</t>
+          <t>15,96; 49,95</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 20,37</t>
+          <t>-16,36; 21,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-57,3; -32,65</t>
+          <t>-56,8; -33,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,91; 21,27</t>
+          <t>6,56; 21,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-23,86; -5,24</t>
+          <t>-24,37; -5,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-79,38; -64,68</t>
+          <t>-78,69; -64,65</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11,11; 28,24</t>
+          <t>11,03; 27,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 7,61</t>
+          <t>-12,57; 8,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-70,02; -53,62</t>
+          <t>-70,64; -53,61</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,78; 22,68</t>
+          <t>11,6; 22,81</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -1,56</t>
+          <t>-15,58; -1,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-73,57; -62,18</t>
+          <t>-72,48; -61,34</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>8,28; 29,66</t>
+          <t>7,82; 29,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-28,51; -6,95</t>
+          <t>-29,35; -7,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-95,58; -86,13</t>
+          <t>-95,77; -86,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,85; 45,57</t>
+          <t>14,86; 45,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 12,15</t>
+          <t>-16,76; 12,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-95,22; -83,63</t>
+          <t>-95,18; -83,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,62; 32,28</t>
+          <t>14,74; 32,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,72; -2,21</t>
+          <t>-19,84; -1,94</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-94,67; -87,47</t>
+          <t>-94,49; -87,48</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>23,77; 43,27</t>
+          <t>23,57; 42,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>30,88; 49,14</t>
+          <t>30,3; 48,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16,31; 36,95</t>
+          <t>16,63; 35,92</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15,88; 34,53</t>
+          <t>15,19; 33,73</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>17,93; 35,44</t>
+          <t>17,69; 35,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,0; 28,5</t>
+          <t>8,66; 27,88</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,09; 35,5</t>
+          <t>21,76; 35,01</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>26,52; 39,8</t>
+          <t>26,43; 39,21</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>15,33; 29,73</t>
+          <t>15,14; 28,77</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>38,98; 96,54</t>
+          <t>39,34; 93,04</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>50,65; 111,42</t>
+          <t>49,24; 104,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27,6; 80,66</t>
+          <t>27,86; 75,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22,75; 64,39</t>
+          <t>22,51; 61,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26,24; 64,4</t>
+          <t>25,42; 64,17</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,94; 50,77</t>
+          <t>12,36; 50,18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,07; 66,9</t>
+          <t>34,77; 66,16</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>42,06; 76,85</t>
+          <t>42,15; 74,34</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24,6; 55,93</t>
+          <t>24,62; 54,71</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,16</t>
+          <t>16,71; 24,87</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 7,93</t>
+          <t>-0,83; 8,19</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-45,04; -35,21</t>
+          <t>-45,23; -35,46</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,75</t>
+          <t>14,87; 23,31</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,4</t>
+          <t>2,38; 11,13</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -30,72</t>
+          <t>-40,55; -31,04</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,39</t>
+          <t>16,88; 22,27</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,06</t>
+          <t>1,87; 7,94</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-41,31; -34,19</t>
+          <t>-41,14; -34,49</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>22,31; 36,13</t>
+          <t>23,23; 37,78</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 11,88</t>
+          <t>-1,16; 12,21</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-63,35; -51,8</t>
+          <t>-63,6; -52,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20,83; 34,33</t>
+          <t>20,68; 35,26</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>3,19; 17,39</t>
+          <t>3,41; 16,93</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-56,98; -45,79</t>
+          <t>-57,48; -46,15</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,69; 33,24</t>
+          <t>23,74; 33,12</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,69; 11,85</t>
+          <t>2,65; 11,78</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-58,68; -50,46</t>
+          <t>-58,81; -50,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-9,48</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-75,93</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-13,2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-65,48</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-9,48</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-76,22</t>
+          <t>-72,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-71,06</t>
+          <t>-74,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 23,47</t>
+          <t>4,98; 23,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 1,3</t>
+          <t>-22,35; 2,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-78,73; -44,79</t>
+          <t>-84,44; -65,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 23,43</t>
+          <t>2,48; 22,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 3,63</t>
+          <t>-26,15; 2,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-84,75; -64,86</t>
+          <t>-82,34; -60,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 20,47</t>
+          <t>7,26; 20,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,76; -2,47</t>
+          <t>-20,88; -2,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-78,71; -57,66</t>
+          <t>-81,17; -66,8</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-11,2%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-89,74%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>14,95%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-15,82%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-78,49%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-11,2%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-90,09%</t>
+          <t>-87,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-84,56%</t>
+          <t>-88,55%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 31,79</t>
+          <t>5,54; 30,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 1,87</t>
+          <t>-25,51; 2,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,9; -55,02</t>
+          <t>-95,15; -81,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 32,02</t>
+          <t>3,33; 30,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 4,77</t>
+          <t>-29,93; 3,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-94,83; -81,88</t>
+          <t>-93,32; -77,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 26,75</t>
+          <t>8,18; 27,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,98; -3,26</t>
+          <t>-24,27; -3,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,12; -69,67</t>
+          <t>-93,0; -82,36</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41,09</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,9</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-29,93</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>32,04</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>10,51</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-41,34</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41,09</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,9</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-29,39</t>
+          <t>-38,09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-35,43</t>
+          <t>-34,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,99; 43,8</t>
+          <t>29,15; 51,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 23,95</t>
+          <t>6,73; 31,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-54,93; -29,71</t>
+          <t>-41,09; -18,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,24; 53,84</t>
+          <t>19,88; 43,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 32,58</t>
+          <t>-2,89; 22,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,61; -17,29</t>
+          <t>-48,61; -26,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,15; 44,54</t>
+          <t>27,94; 44,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 24,5</t>
+          <t>5,21; 22,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-44,03; -26,31</t>
+          <t>-42,5; -25,28</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-60,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>57,9%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>18,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-74,71%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>83,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,42%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-59,74%</t>
+          <t>-68,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-67,71%</t>
+          <t>-64,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,49; 98,13</t>
+          <t>50,82; 129,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 52,1</t>
+          <t>11,47; 76,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,62; -60,54</t>
+          <t>-73,53; -42,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53,34; 140,88</t>
+          <t>32,75; 96,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 84,41</t>
+          <t>-4,64; 47,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,38; -39,28</t>
+          <t>-79,03; -53,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,94; 98,28</t>
+          <t>48,87; 96,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 51,64</t>
+          <t>9,56; 49,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-78,71; -56,15</t>
+          <t>-74,16; -52,58</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-17,12</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-62,21</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>20,84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-6,45</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-54,5</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,3</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-17,12</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-61,81</t>
+          <t>-54,45</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-58,29</t>
+          <t>-58,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 32,78</t>
+          <t>2,58; 21,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 7,17</t>
+          <t>-29,98; -4,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-65,9; -42,37</t>
+          <t>-71,72; -51,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 22,45</t>
+          <t>9,47; 31,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,95; -4,49</t>
+          <t>-21,5; 8,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,74; -50,41</t>
+          <t>-65,91; -41,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 23,94</t>
+          <t>8,7; 23,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,51; -3,15</t>
+          <t>-21,74; -2,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-65,29; -49,62</t>
+          <t>-65,93; -49,74</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16,08%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-22,38%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-81,34%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>29,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-9,09%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-76,79%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16,08%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-22,38%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-80,83%</t>
+          <t>-76,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-78,99%</t>
+          <t>-79,17%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,58; 53,89</t>
+          <t>3,24; 31,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 10,68</t>
+          <t>-37,88; -6,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,41; -64,37</t>
+          <t>-89,89; -70,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 31,74</t>
+          <t>12,1; 49,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,24; -6,28</t>
+          <t>-28,79; 13,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,21; -70,36</t>
+          <t>-85,86; -64,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,81; 34,51</t>
+          <t>11,21; 34,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,6; -4,56</t>
+          <t>-28,08; -4,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,54; -71,3</t>
+          <t>-85,78; -71,65</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-35,45</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-24,11</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-50,38</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,7</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-34,07</t>
+          <t>-50,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-41,79</t>
+          <t>-43,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 18,36</t>
+          <t>-12,74; 11,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-38,29; -9,34</t>
+          <t>-14,64; 10,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-62,4; -37,15</t>
+          <t>-50,25; -13,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 12,17</t>
+          <t>-4,92; 17,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 9,9</t>
+          <t>-38,49; -8,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,49; -9,83</t>
+          <t>-61,81; -36,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 10,51</t>
+          <t>-5,88; 11,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-22,63; -2,68</t>
+          <t>-22,34; -3,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-51,62; -26,05</t>
+          <t>-52,13; -27,89</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-2,13%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-44,36%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>7,66%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-30,25%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-63,21%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-2,13%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-42,64%</t>
+          <t>-63,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-52,35%</t>
+          <t>-53,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 25,23</t>
+          <t>-15,34; 16,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,4; -13,09</t>
+          <t>-17,52; 13,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,6; -48,61</t>
+          <t>-61,42; -18,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 16,28</t>
+          <t>-5,67; 23,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 13,05</t>
+          <t>-46,78; -12,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,32; -12,98</t>
+          <t>-73,75; -48,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 13,82</t>
+          <t>-7,01; 14,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,49; -3,6</t>
+          <t>-27,1; -4,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,21; -33,31</t>
+          <t>-64,26; -36,22</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>34,19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>47,6</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-17,62</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>13,21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>15,78</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-52,8</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34,19</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>47,6</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-15,53</t>
+          <t>-52,13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-32,54</t>
+          <t>-33,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 43,79</t>
+          <t>6,76; 61,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 44,56</t>
+          <t>22,48; 71,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-72,63; -19,41</t>
+          <t>-45,11; 11,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,28; 58,85</t>
+          <t>-7,34; 44,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,64; 68,94</t>
+          <t>-3,24; 43,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 11,6</t>
+          <t>-71,33; -17,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,95; 45,36</t>
+          <t>5,79; 44,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,24; 53,33</t>
+          <t>16,06; 51,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-50,4; -12,65</t>
+          <t>-51,31; -14,03</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>69,87%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-36,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>17,03%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>20,34%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-68,06%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>69,87%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,74%</t>
+          <t>-67,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-52,49%</t>
+          <t>-53,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 78,89</t>
+          <t>9,37; 243,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 90,44</t>
+          <t>30,39; 299,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,78; -44,32</t>
+          <t>-64,22; 58,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,24; 220,04</t>
+          <t>-8,3; 87,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,11; 250,79</t>
+          <t>-3,57; 79,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,49; 38,56</t>
+          <t>-80,63; -38,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,08; 101,77</t>
+          <t>8,02; 95,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>22,69; 125,47</t>
+          <t>20,71; 113,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-67,97; -28,26</t>
+          <t>-69,31; -29,24</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>18,98</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6,27</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-28,69</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>23,65</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-5,13</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-36,56</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,27</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-27,06</t>
+          <t>-39,05</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-31,34</t>
+          <t>-33,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10,68; 35,98</t>
+          <t>5,27; 31,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 13,55</t>
+          <t>-14,57; 20,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-51,38; -22,32</t>
+          <t>-41,97; -13,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,35; 31,91</t>
+          <t>9,89; 36,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 21,95</t>
+          <t>-24,63; 13,79</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-41,25; -13,22</t>
+          <t>-52,89; -24,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,7; 30,38</t>
+          <t>11,99; 30,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 13,76</t>
+          <t>-11,98; 14,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-40,63; -21,23</t>
+          <t>-44,16; -23,81</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-41,91%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>34,82%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-7,55%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-53,84%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-39,53%</t>
+          <t>-57,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-45,95%</t>
+          <t>-49,42%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14,48; 62,56</t>
+          <t>7,21; 55,24</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 21,86</t>
+          <t>-18,93; 34,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-68,62; -36,0</t>
+          <t>-57,46; -23,27</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8,56; 54,04</t>
+          <t>12,91; 64,18</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 34,88</t>
+          <t>-34,12; 22,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-55,24; -21,34</t>
+          <t>-72,02; -39,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,96; 49,95</t>
+          <t>16,52; 50,69</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 21,51</t>
+          <t>-16,6; 22,19</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-56,8; -33,65</t>
+          <t>-61,03; -37,71</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>20,03</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,95</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-62,73</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>13,81</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-14,84</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-72,57</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>20,03</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,95</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-62,58</t>
+          <t>-72,39</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,56; 21,51</t>
+          <t>11,73; 29,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-24,37; -5,43</t>
+          <t>-13,18; 8,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-78,69; -64,65</t>
+          <t>-69,86; -54,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11,03; 27,93</t>
+          <t>6,04; 21,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 8,06</t>
+          <t>-24,94; -5,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-70,64; -53,61</t>
+          <t>-79,93; -64,82</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,6; 22,81</t>
+          <t>11,59; 22,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -1,52</t>
+          <t>-15,77; -1,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-72,48; -61,34</t>
+          <t>-72,5; -62,08</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-2,83%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-91,1%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>17,5%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-18,8%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-91,95%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-2,83%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-90,87%</t>
+          <t>-91,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,82; 29,75</t>
+          <t>16,02; 47,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,35; -7,04</t>
+          <t>-17,84; 13,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-95,77; -86,39</t>
+          <t>-95,2; -83,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,86; 45,4</t>
+          <t>7,18; 29,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 12,75</t>
+          <t>-29,98; -7,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-95,18; -83,35</t>
+          <t>-95,58; -86,61</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,74; 32,72</t>
+          <t>14,92; 32,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-19,84; -1,94</t>
+          <t>-20,84; -2,12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-94,49; -87,48</t>
+          <t>-94,55; -86,96</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>24,56</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>26,92</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>18,15</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>33,49</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>39,26</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>26,64</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>24,56</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>26,92</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,47</t>
+          <t>25,55</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>22,43</t>
+          <t>21,75</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>23,57; 42,51</t>
+          <t>15,31; 33,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>30,3; 48,1</t>
+          <t>18,17; 36,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16,63; 35,92</t>
+          <t>8,3; 27,52</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15,19; 33,73</t>
+          <t>23,22; 43,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>17,69; 35,42</t>
+          <t>30,6; 49,24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,66; 27,88</t>
+          <t>14,13; 35,89</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,76; 35,01</t>
+          <t>22,11; 36,43</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>26,43; 39,21</t>
+          <t>26,54; 39,56</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>15,14; 28,77</t>
+          <t>14,59; 29,08</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>39,36%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>43,14%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>62,43%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>73,19%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>49,67%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>39,36%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>43,14%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>39,34; 93,04</t>
+          <t>22,18; 59,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>49,24; 104,03</t>
+          <t>26,39; 64,96</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27,86; 75,62</t>
+          <t>12,19; 50,23</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22,51; 61,05</t>
+          <t>38,41; 96,32</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>25,42; 64,17</t>
+          <t>49,64; 108,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,36; 50,18</t>
+          <t>23,69; 78,13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,77; 66,16</t>
+          <t>35,24; 71,71</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>42,15; 74,34</t>
+          <t>41,91; 75,32</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24,62; 54,71</t>
+          <t>23,1; 54,82</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>19,08</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>6,79</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-34,96</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>20,25</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>3,34</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-39,99</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>19,08</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>6,79</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-35,89</t>
+          <t>-38,71</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-37,82</t>
+          <t>-36,75</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>16,71; 24,87</t>
+          <t>14,65; 22,76</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,19</t>
+          <t>1,75; 10,92</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-45,23; -35,46</t>
+          <t>-39,27; -29,82</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14,87; 23,31</t>
+          <t>16,35; 24,1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,38; 11,13</t>
+          <t>-1,32; 7,73</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-40,55; -31,04</t>
+          <t>-43,16; -34,1</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,88; 22,27</t>
+          <t>16,89; 22,53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,94</t>
+          <t>1,89; 8,52</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -34,49</t>
+          <t>-39,89; -33,42</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-50,8%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>29,07%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-57,39%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>27,71%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-52,14%</t>
+          <t>-55,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-54,61%</t>
+          <t>-53,07%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>23,23; 37,78</t>
+          <t>20,51; 34,68</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 12,21</t>
+          <t>2,44; 16,38</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-63,6; -52,0</t>
+          <t>-56,01; -44,6</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20,68; 35,26</t>
+          <t>22,77; 36,14</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>3,41; 16,93</t>
+          <t>-1,87; 11,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-57,48; -46,15</t>
+          <t>-60,25; -50,56</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,12</t>
+          <t>23,7; 33,57</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,78</t>
+          <t>2,68; 12,57</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-58,81; -50,76</t>
+          <t>-56,93; -49,51</t>
         </is>
       </c>
     </row>
